--- a/LoanOfficer-A/2026/180 ayangpalli ibeyaima.xlsx
+++ b/LoanOfficer-A/2026/180 ayangpalli ibeyaima.xlsx
@@ -829,7 +829,7 @@
       </c>
       <c r="K1" s="15">
         <f>17-K2</f>
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L1" s="13"/>
       <c r="M1" s="11"/>
@@ -838,7 +838,7 @@
       </c>
       <c r="O1" s="12">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>0</v>
+        <v>2100</v>
       </c>
       <c r="P1" s="16"/>
     </row>
@@ -858,7 +858,7 @@
       </c>
       <c r="G2" s="19">
         <f>B3+G1*7</f>
-        <v>119</v>
+        <v>46297</v>
       </c>
       <c r="H2" s="13"/>
       <c r="I2" s="13"/>
@@ -867,7 +867,7 @@
       </c>
       <c r="K2" s="15">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L2" s="13"/>
       <c r="M2" s="11"/>
@@ -876,7 +876,7 @@
       </c>
       <c r="O2" s="18">
         <f>C2-O1</f>
-        <v>35700</v>
+        <v>33600</v>
       </c>
       <c r="P2" s="16"/>
     </row>
@@ -884,9 +884,15 @@
       <c r="A3" s="20">
         <v>1</v>
       </c>
-      <c r="B3" s="21"/>
-      <c r="C3" s="22"/>
-      <c r="D3" s="20"/>
+      <c r="B3" s="21">
+        <v>46178</v>
+      </c>
+      <c r="C3" s="22">
+        <v>2100</v>
+      </c>
+      <c r="D3" s="20">
+        <v>1</v>
+      </c>
       <c r="E3" s="20">
         <v>31</v>
       </c>
